--- a/Hardware/Controller/JLC_PCBA_BOM-DALI_EVG_Controller(V0.1).xlsx
+++ b/Hardware/Controller/JLC_PCBA_BOM-DALI_EVG_Controller(V0.1).xlsx
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="0" defaultRowHeight="12.75"/>
   <cols>
     <col width="20.2109375" customWidth="1" style="33" min="1" max="2"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="D2" s="21" t="inlineStr">
         <is>
-          <t>C1, C11, C13, C14, C15</t>
+          <t>C1, C3, C11, C13, C14, C15</t>
         </is>
       </c>
       <c r="E2" s="21" t="inlineStr">
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1427,67 +1427,63 @@
     <row r="30">
       <c r="A30" s="29" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B30" s="22" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C30" s="22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="n"/>
       <c r="D30" s="22" t="inlineStr">
         <is>
-          <t>R19, R20</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>R0603</t>
         </is>
       </c>
       <c r="F30" s="30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="29" t="inlineStr">
         <is>
-          <t>1.5k</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>Resistor</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
         <is>
-          <t>1.5k</t>
+          <t>100</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
         <is>
-          <t>R21</t>
+          <t>R19, R20</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
         <is>
-          <t>R0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F31" s="30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.5k</t>
         </is>
       </c>
       <c r="B32" s="22" t="inlineStr">
@@ -1495,10 +1491,14 @@
           <t>Resistor</t>
         </is>
       </c>
-      <c r="C32" s="22" t="n"/>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>1.5k</t>
+        </is>
+      </c>
       <c r="D32" s="22" t="inlineStr">
         <is>
-          <t>R27, R42</t>
+          <t>R21</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="F32" s="30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="29" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B33" s="22" t="inlineStr">
@@ -1524,7 +1524,7 @@
       <c r="C33" s="22" t="n"/>
       <c r="D33" s="22" t="inlineStr">
         <is>
-          <t>R28</t>
+          <t>R27, R42</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F33" s="30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="29" t="inlineStr">
         <is>
-          <t>330k</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="B34" s="22" t="inlineStr">
@@ -1550,7 +1550,7 @@
       <c r="C34" s="22" t="n"/>
       <c r="D34" s="22" t="inlineStr">
         <is>
-          <t>R31</t>
+          <t>R28</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -1565,7 +1565,7 @@
     <row r="35">
       <c r="A35" s="29" t="inlineStr">
         <is>
-          <t>220k</t>
+          <t>330k</t>
         </is>
       </c>
       <c r="B35" s="22" t="inlineStr">
@@ -1576,7 +1576,7 @@
       <c r="C35" s="22" t="n"/>
       <c r="D35" s="22" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R31</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -1591,7 +1591,7 @@
     <row r="36">
       <c r="A36" s="29" t="inlineStr">
         <is>
-          <t>20k</t>
+          <t>220k</t>
         </is>
       </c>
       <c r="B36" s="22" t="inlineStr">
@@ -1602,7 +1602,7 @@
       <c r="C36" s="22" t="n"/>
       <c r="D36" s="22" t="inlineStr">
         <is>
-          <t>R33</t>
+          <t>R32</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="37">
       <c r="A37" s="29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20k</t>
         </is>
       </c>
       <c r="B37" s="22" t="inlineStr">
@@ -1628,7 +1628,7 @@
       <c r="C37" s="22" t="n"/>
       <c r="D37" s="22" t="inlineStr">
         <is>
-          <t>R41</t>
+          <t>R33</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -1643,7 +1643,7 @@
     <row r="38">
       <c r="A38" s="29" t="inlineStr">
         <is>
-          <t>47k</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B38" s="22" t="inlineStr">
@@ -1654,12 +1654,12 @@
       <c r="C38" s="22" t="n"/>
       <c r="D38" s="22" t="inlineStr">
         <is>
-          <t>R46</t>
+          <t>R41</t>
         </is>
       </c>
       <c r="E38" s="22" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>R0603</t>
         </is>
       </c>
       <c r="F38" s="30" t="n">
@@ -1669,23 +1669,23 @@
     <row r="39">
       <c r="A39" s="29" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>47k</t>
         </is>
       </c>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>Circuit Breaker</t>
+          <t>Resistor</t>
         </is>
       </c>
       <c r="C39" s="22" t="n"/>
       <c r="D39" s="22" t="inlineStr">
         <is>
-          <t>SB1</t>
+          <t>R46</t>
         </is>
       </c>
       <c r="E39" s="22" t="inlineStr">
         <is>
-          <t>SB_0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F39" s="30" t="n">
@@ -1695,23 +1695,23 @@
     <row r="40">
       <c r="A40" s="29" t="inlineStr">
         <is>
-          <t>CH32V003F4P6</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>RISC-V microcontroller</t>
+          <t>Circuit Breaker</t>
         </is>
       </c>
       <c r="C40" s="22" t="n"/>
       <c r="D40" s="22" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>SB1</t>
         </is>
       </c>
       <c r="E40" s="22" t="inlineStr">
         <is>
-          <t>SOP65P640X121-20N</t>
+          <t>SB_0603</t>
         </is>
       </c>
       <c r="F40" s="30" t="n">
@@ -1721,23 +1721,23 @@
     <row r="41">
       <c r="A41" s="29" t="inlineStr">
         <is>
-          <t>LM393DR2G</t>
+          <t>CH32V003F4P6</t>
         </is>
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>Comparator General Purpose CMOS, DTL, ECL, MOS, Open-Collector, TTL 8-SOIC</t>
+          <t>RISC-V microcontroller</t>
         </is>
       </c>
       <c r="C41" s="22" t="n"/>
       <c r="D41" s="22" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="E41" s="22" t="inlineStr">
         <is>
-          <t>SOIC127P600X265-8N (SOIC-8)</t>
+          <t>SOP65P640X121-20N</t>
         </is>
       </c>
       <c r="F41" s="30" t="n">
@@ -1747,26 +1747,52 @@
     <row r="42">
       <c r="A42" s="29" t="inlineStr">
         <is>
-          <t>EEPROM I2C</t>
+          <t>LM393DR2G</t>
         </is>
       </c>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>EEPROM I2C</t>
+          <t>Comparator General Purpose CMOS, DTL, ECL, MOS, Open-Collector, TTL 8-SOIC</t>
         </is>
       </c>
       <c r="C42" s="22" t="n"/>
       <c r="D42" s="22" t="inlineStr">
         <is>
+          <t>U2</t>
+        </is>
+      </c>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>SOIC127P600X265-8N (SOIC-8)</t>
+        </is>
+      </c>
+      <c r="F42" s="30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="29" t="inlineStr">
+        <is>
+          <t>M24C64-RMN6TP</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>M24C64-RMN6TP</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="22" t="inlineStr">
+        <is>
           <t>U3</t>
         </is>
       </c>
-      <c r="E42" s="22" t="inlineStr">
+      <c r="E43" s="22" t="inlineStr">
         <is>
           <t>SOIC127P600X265-8N (SOIC-8)</t>
         </is>
       </c>
-      <c r="F42" s="30" t="n">
+      <c r="F43" s="30" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Hardware/Controller/JLC_PCBA_BOM-DALI_EVG_Controller(V0.1).xlsx
+++ b/Hardware/Controller/JLC_PCBA_BOM-DALI_EVG_Controller(V0.1).xlsx
@@ -957,7 +957,7 @@
       <c r="C12" s="22" t="n"/>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>D6, D7, D8, D9</t>
+          <t>D6, D8, D9</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="F12" s="30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1051,12 +1051,12 @@
     <row r="16">
       <c r="A16" s="29" t="inlineStr">
         <is>
-          <t>Header 1x9</t>
+          <t>C262302</t>
         </is>
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>Header 1x9</t>
+          <t>FFC/FPC Connector 10 Position 0.5mm Pitch Single-side Contact/Vertical Surface Mount</t>
         </is>
       </c>
       <c r="C16" s="22" t="n"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>Header 1x9</t>
+          <t>CONN-TH-10P_AFC11-S10ICC-00</t>
         </is>
       </c>
       <c r="F16" s="30" t="n">
@@ -1524,7 +1524,7 @@
       <c r="C33" s="22" t="n"/>
       <c r="D33" s="22" t="inlineStr">
         <is>
-          <t>R27, R42</t>
+          <t>R27</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F33" s="30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1773,12 +1773,12 @@
     <row r="43">
       <c r="A43" s="29" t="inlineStr">
         <is>
-          <t>M24C64-RMN6TP</t>
+          <t>AT24C256C-SSHL-T</t>
         </is>
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>M24C64-RMN6TP</t>
+          <t>AT24C256C-SSHL-T</t>
         </is>
       </c>
       <c r="C43" s="22" t="n"/>
